--- a/output/pdf_financials_xlsx/IQ.xlsx
+++ b/output/pdf_financials_xlsx/IQ.xlsx
@@ -861,40 +861,40 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3.298</v>
+        <v>3.297</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.324</v>
+        <v>1.986</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.229</v>
+        <v>1.88</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.22</v>
+        <v>1.825</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.184</v>
+        <v>1.308</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.102</v>
+        <v>1.327</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.097</v>
+        <v>1.254</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.111</v>
+        <v>1.521</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.129</v>
+        <v>1.624</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.14</v>
+        <v>1.65</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.109</v>
+        <v>1.551</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.118</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="11">
@@ -912,40 +912,40 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.025</v>
+        <v>-1.024</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.442</v>
+        <v>-0.22</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.342</v>
+        <v>-0.309</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.358</v>
+        <v>-0.247</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1.483</v>
+        <v>0.359</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.749</v>
+        <v>0.524</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.689</v>
+        <v>0.532</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.873</v>
+        <v>0.463</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.978</v>
+        <v>0.483</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>2.417</v>
+        <v>0.907</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.385</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.561</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="12">
@@ -990,13 +990,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="13">
@@ -1821,13 +1821,13 @@
         <v>0.231</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.713</v>
+        <v>0.726</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.449</v>
+        <v>0.459</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="28">
@@ -1923,13 +1923,13 @@
         <v>0.458</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.039</v>
+        <v>1.052</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.761</v>
+        <v>0.771</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.873</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="30">
@@ -1974,13 +1974,13 @@
         <v>12.43889190657251</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>20.61507936507936</v>
+        <v>20.87301587301587</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>20.52319309600863</v>
+        <v>20.79288025889968</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>19.97711670480549</v>
+        <v>20.02288329519451</v>
       </c>
     </row>
     <row r="31">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.744</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.744</v>
@@ -2123,10 +2123,10 @@
         <v>0.108</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.527</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.717</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.744</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.744</v>
@@ -2221,10 +2221,10 @@
         <v>0.108</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.527</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.717</v>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.648</v>
+        <v>0.904</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.395</v>
@@ -2809,10 +2809,10 @@
         <v>0.352</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.479</v>
+        <v>0.347</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.047</v>
@@ -6630,13 +6630,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="125">
@@ -6681,13 +6681,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="126">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -19732,7 +19732,11 @@
           <t>Lease payments (note 13)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -32334,7 +32338,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -32502,7 +32506,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -32588,7 +32592,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -33490,7 +33494,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -33918,7 +33922,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -34002,7 +34006,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -34424,7 +34428,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -35696,7 +35700,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -36126,7 +36130,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -36910,7 +36914,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -37776,7 +37780,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -38538,7 +38542,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -38794,7 +38798,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -39136,7 +39140,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -39310,7 +39314,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -40430,7 +40434,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E396" s="5" t="n">

--- a/output/pdf_financials_xlsx/IQ.xlsx
+++ b/output/pdf_financials_xlsx/IQ.xlsx
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.211</v>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
@@ -5357,40 +5357,40 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.277</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.431</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="101">
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -18618,7 +18618,11 @@
           <t>Depreciation of property, plant and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -18692,7 +18696,11 @@
           <t>Depreciation of right-of-use asset (note 13)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -23712,7 +23720,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -25996,7 +26008,11 @@
           <t>Depreciation of property, plant and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -26998,7 +27014,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -28014,7 +28034,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -28698,7 +28722,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E258" s="5" t="n">
@@ -29476,7 +29500,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IQ.xlsx
+++ b/output/pdf_financials_xlsx/IQ.xlsx
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.135</v>
+        <v>-3.316</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-1.262</v>
+        <v>-1.263</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.31</v>
@@ -3924,13 +3924,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="71">
@@ -3973,13 +3973,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="72">
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4316,13 +4316,13 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="79">
@@ -4365,13 +4365,13 @@
         <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="80">
@@ -4435,20 +4435,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.04221061792863359</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.02830882352941176</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.01705083675402589</v>
       </c>
     </row>
     <row r="81">
@@ -4687,13 +4681,13 @@
         <v>0.1</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.201</v>
+        <v>0.124</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0.124</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>0.106</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="86">
@@ -5298,7 +5292,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.135</v>
+        <v>-3.316</v>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
@@ -6023,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="F113" s="3" t="n">
         <v>0</v>
@@ -8464,7 +8458,11 @@
           <t>Lease obligations (note 13)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -8700,7 +8698,11 @@
           <t>Lease obligations (note 13)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -24818,7 +24820,11 @@
           <t>Proceeds from issuance of common shares pursuant to private placement</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -24900,7 +24906,11 @@
           <t>Costs of issuance of common shares pursuant to private placement</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -27182,7 +27192,11 @@
           <t>Acquisition of business (note 9)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -28464,7 +28478,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E255" s="5" t="n">
         <v>-3.316</v>
       </c>
@@ -40806,7 +40824,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E400" s="5" t="n">
         <v>-3.316</v>
       </c>
